--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1035,23 +1035,23 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46174</v>
+        <v>46277</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>P-2</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46368</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>P-2</t>
-        </is>
-      </c>
       <c r="F21" s="1" t="n">
-        <v>46266</v>
+        <v>47008</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>45839</v>
+        <v>46279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46204</v>
+        <v>46644</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>45901</v>
+        <v>46290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46266</v>
+        <v>46655</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46174</v>
+        <v>46295</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>P-2</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46386</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>P-3</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P-2</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46251</v>
+        <v>46220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46343</v>
+        <v>46312</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -10,6 +10,7 @@
     <sheet name="KBS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="LS06" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Radiostanice" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ETCS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2542,4 +2543,50 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Číslo mašiny</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Datum provedení</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rozsah</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Příští prohlídka</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>844 003</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2582,7 +2582,9 @@
           <t>844 003</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" s="1" t="n">
+        <v>45931</v>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
     </row>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2586,7 +2586,9 @@
         <v>45931</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="1" t="n">
+        <v>46113</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2590,6 +2590,20 @@
         <v>46113</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>844 013</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="1" t="n">
+        <v>46092</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2604,6 +2604,20 @@
         <v>46092</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>844 014</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45691</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="1" t="n">
+        <v>45872</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2618,6 +2618,20 @@
         <v>45872</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>844 015</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" s="1" t="n">
+        <v>46480</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,6 +2632,20 @@
         <v>46480</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>844 020</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" s="1" t="n">
+        <v>46480</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2646,6 +2646,20 @@
         <v>46480</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>844 021</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="1" t="n">
+        <v>46480</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2660,6 +2660,20 @@
         <v>46480</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>844 022</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="1" t="n">
+        <v>46479</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2674,6 +2674,52 @@
         <v>46479</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>844 025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>844 026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>844 027</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>844 028</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2680,9 +2680,13 @@
           <t>844 025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" s="1" t="n">
+        <v>45691</v>
+      </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" s="1" t="n">
+        <v>45872</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2690,9 +2694,13 @@
           <t>844 026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" s="1" t="n">
+        <v>46298</v>
+      </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="1" t="n">
+        <v>46480</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2700,9 +2708,13 @@
           <t>844 027</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" s="1" t="n">
+        <v>46298</v>
+      </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" s="1" t="n">
+        <v>46480</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2710,9 +2722,13 @@
           <t>844 028</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" s="1" t="n">
+        <v>46304</v>
+      </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" s="1" t="n">
+        <v>46486</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -2720,6 +2736,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2731,10 +2731,18 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>844 029</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46296</v>
+      </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" s="1" t="n">
+        <v>46478</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -2742,6 +2750,62 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>842 010</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>842 011</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>842 021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>842 025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>842 035</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,10 +2801,20 @@
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>842 036</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2756,9 +2756,13 @@
           <t>842 010</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" s="1" t="n">
+        <v>46298</v>
+      </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" s="1" t="n">
+        <v>46480</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2766,9 +2770,13 @@
           <t>842 011</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" s="1" t="n">
+        <v>46298</v>
+      </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" s="1" t="n">
+        <v>46480</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2776,9 +2784,13 @@
           <t>842 021</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" s="1" t="n">
+        <v>46301</v>
+      </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" s="1" t="n">
+        <v>46483</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2786,9 +2798,13 @@
           <t>842 025</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" s="1" t="n">
+        <v>46297</v>
+      </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" s="1" t="n">
+        <v>46479</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2796,9 +2812,13 @@
           <t>842 035</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" s="1" t="n">
+        <v>46297</v>
+      </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" s="1" t="n">
+        <v>46479</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2806,9 +2826,13 @@
           <t>842 036</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" s="1" t="n">
+        <v>46297</v>
+      </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" s="1" t="n">
+        <v>46479</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2840,6 +2840,66 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>80 29 210</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>80 29 211</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>80 29 212</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>80 29 213</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>80 29 214</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>80 29 218</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2799,11 +2799,11 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46297</v>
+        <v>45751</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" s="1" t="n">
-        <v>46479</v>
+        <v>45934</v>
       </c>
     </row>
     <row r="19">
@@ -2846,9 +2846,13 @@
           <t>80 29 210</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" s="1" t="n">
+        <v>46298</v>
+      </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" s="1" t="n">
+        <v>46480</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2856,9 +2860,13 @@
           <t>80 29 211</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" s="1" t="n">
+        <v>46298</v>
+      </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" s="1" t="n">
+        <v>46480</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2866,9 +2874,13 @@
           <t>80 29 212</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" s="1" t="n">
+        <v>46298</v>
+      </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" s="1" t="n">
+        <v>46480</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2876,9 +2888,13 @@
           <t>80 29 213</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" s="1" t="n">
+        <v>46298</v>
+      </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" s="1" t="n">
+        <v>46480</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2886,9 +2902,13 @@
           <t>80 29 214</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" s="1" t="n">
+        <v>46297</v>
+      </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" s="1" t="n">
+        <v>46479</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2896,9 +2916,13 @@
           <t>80 29 218</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" s="1" t="n">
+        <v>45691</v>
+      </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" s="1" t="n">
+        <v>45872</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2611,11 +2611,11 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>45691</v>
+        <v>46122</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="1" t="n">
-        <v>45872</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="5">
@@ -2625,11 +2625,11 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46298</v>
+        <v>46150</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="1" t="n">
-        <v>46480</v>
+        <v>46334</v>
       </c>
     </row>
     <row r="6">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2585,7 +2585,11 @@
       <c r="B2" s="1" t="n">
         <v>45931</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D2" s="1" t="n">
         <v>46113</v>
       </c>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2603,7 +2603,11 @@
       <c r="B3" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D3" s="1" t="n">
         <v>46092</v>
       </c>
@@ -2617,7 +2621,11 @@
       <c r="B4" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D4" s="1" t="n">
         <v>46305</v>
       </c>
@@ -2631,7 +2639,11 @@
       <c r="B5" s="1" t="n">
         <v>46150</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D5" s="1" t="n">
         <v>46334</v>
       </c>
@@ -2645,7 +2657,11 @@
       <c r="B6" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D6" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2659,7 +2675,11 @@
       <c r="B7" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D7" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2673,7 +2693,11 @@
       <c r="B8" s="1" t="n">
         <v>46297</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D8" s="1" t="n">
         <v>46479</v>
       </c>
@@ -2687,7 +2711,11 @@
       <c r="B9" s="1" t="n">
         <v>45691</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D9" s="1" t="n">
         <v>45872</v>
       </c>
@@ -2701,7 +2729,11 @@
       <c r="B10" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D10" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2715,7 +2747,11 @@
       <c r="B11" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D11" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2729,7 +2765,11 @@
       <c r="B12" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D12" s="1" t="n">
         <v>46486</v>
       </c>
@@ -2743,7 +2783,11 @@
       <c r="B13" s="1" t="n">
         <v>46296</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D13" s="1" t="n">
         <v>46478</v>
       </c>
@@ -2763,7 +2807,11 @@
       <c r="B15" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D15" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2777,7 +2825,11 @@
       <c r="B16" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D16" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2791,7 +2843,11 @@
       <c r="B17" s="1" t="n">
         <v>46301</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D17" s="1" t="n">
         <v>46483</v>
       </c>
@@ -2805,7 +2861,11 @@
       <c r="B18" s="1" t="n">
         <v>45751</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D18" s="1" t="n">
         <v>45934</v>
       </c>
@@ -2819,7 +2879,11 @@
       <c r="B19" s="1" t="n">
         <v>46297</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D19" s="1" t="n">
         <v>46479</v>
       </c>
@@ -2833,7 +2897,11 @@
       <c r="B20" s="1" t="n">
         <v>46297</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D20" s="1" t="n">
         <v>46479</v>
       </c>
@@ -2853,7 +2921,11 @@
       <c r="B22" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D22" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2867,7 +2939,11 @@
       <c r="B23" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D23" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2881,7 +2957,11 @@
       <c r="B24" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D24" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2895,7 +2975,11 @@
       <c r="B25" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D25" s="1" t="n">
         <v>46480</v>
       </c>
@@ -2909,7 +2993,11 @@
       <c r="B26" s="1" t="n">
         <v>46297</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D26" s="1" t="n">
         <v>46479</v>
       </c>
@@ -2923,7 +3011,11 @@
       <c r="B27" s="1" t="n">
         <v>45691</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Vizuální prohlídka</t>
+        </is>
+      </c>
       <c r="D27" s="1" t="n">
         <v>45872</v>
       </c>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>45931</v>
+        <v>46298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46113</v>
+        <v>46480</v>
       </c>
     </row>
     <row r="3">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>45911</v>
+        <v>46298</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46092</v>
+        <v>46480</v>
       </c>
     </row>
     <row r="4">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46122</v>
+        <v>46298</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46305</v>
+        <v>46480</v>
       </c>
     </row>
     <row r="5">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46150</v>
+        <v>46298</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46334</v>
+        <v>46480</v>
       </c>
     </row>
     <row r="6">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>45691</v>
+        <v>46298</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45872</v>
+        <v>46480</v>
       </c>
     </row>
     <row r="10">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>45751</v>
+        <v>46298</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45934</v>
+        <v>46480</v>
       </c>
     </row>
     <row r="19">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>45691</v>
+        <v>46298</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45872</v>
+        <v>46480</v>
       </c>
     </row>
   </sheetData>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46298</v>
+        <v>46303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46480</v>
+        <v>46485</v>
       </c>
     </row>
     <row r="3">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46298</v>
+        <v>46059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46480</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="4">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46298</v>
+        <v>46065</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46480</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="5">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46298</v>
+        <v>46065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46480</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="6">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46298</v>
+        <v>46093</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46480</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="7">
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46298</v>
+        <v>46004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46480</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="8">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46297</v>
+        <v>46058</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46479</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="9">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46298</v>
+        <v>46003</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46480</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="10">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46298</v>
+        <v>46030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46480</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="11">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46298</v>
+        <v>46032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46480</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="12">
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46304</v>
+        <v>46038</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46486</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="13">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46296</v>
+        <v>45967</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46478</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="14">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46298</v>
+        <v>46010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46480</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="16">
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46298</v>
+        <v>46030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46480</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="17">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46301</v>
+        <v>46009</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46483</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="18">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46298</v>
+        <v>46031</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46480</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="19">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46297</v>
+        <v>46045</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46479</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="20">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46297</v>
+        <v>46003</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46479</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="21">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46298</v>
+        <v>46010</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46480</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="23">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46298</v>
+        <v>46059</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46480</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="24">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46298</v>
+        <v>46003</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46480</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="26">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1117,7 +1117,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>844003</t>
+          <t>844 003</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -1151,7 +1151,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>844013</t>
+          <t>844 013</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1117,7 +1117,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>844 003</t>
+          <t>844003</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -1151,7 +1151,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>844 013</t>
+          <t>844013</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46093</v>
+        <v>46304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46277</v>
+        <v>46486</v>
       </c>
     </row>
     <row r="7">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46032</v>
+        <v>46304</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46213</v>
+        <v>46486</v>
       </c>
     </row>
     <row r="12">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46298</v>
+        <v>46031</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46480</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="25">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46297</v>
+        <v>46011</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46479</v>
+        <v>46193</v>
       </c>
     </row>
     <row r="27">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46298</v>
+        <v>46303</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46480</v>
+        <v>46485</v>
       </c>
     </row>
   </sheetData>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46174</v>
+        <v>46306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>P-3</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46398</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>P-2</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>P-3</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46220</v>
+        <v>46305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>P-2</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46397</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>P-3</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>P-2</t>
         </is>
       </c>
       <c r="F16" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46296</v>
+        <v>46935</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46296</v>
+        <v>46966</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46204</v>
+        <v>46307</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>P-3</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46399</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>P-2</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P-3</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46030</v>
+        <v>46312</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46211</v>
+        <v>46494</v>
       </c>
     </row>
     <row r="11">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46058</v>
+        <v>46312</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46239</v>
+        <v>46494</v>
       </c>
     </row>
     <row r="9">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46312</v>
+        <v>46307</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46494</v>
+        <v>46489</v>
       </c>
     </row>
     <row r="11">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1007,19 +1007,19 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46204</v>
+        <v>46314</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>P-2</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46406</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>P-3</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>P-2</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46204</v>
+        <v>46311</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>P-2</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46403</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>P-3</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>P-2</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46003</v>
+        <v>46318</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46185</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="21">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46031</v>
+        <v>46318</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46212</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="25">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46011</v>
+        <v>46318</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46193</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="27">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46059</v>
+        <v>46320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46240</v>
+        <v>46502</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46003</v>
+        <v>46320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46185</v>
+        <v>46502</v>
       </c>
     </row>
     <row r="10">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46059</v>
+        <v>46320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46240</v>
+        <v>46502</v>
       </c>
     </row>
     <row r="24">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46003</v>
+        <v>46322</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46185</v>
+        <v>46504</v>
       </c>
     </row>
     <row r="26">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46010</v>
+        <v>46322</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46192</v>
+        <v>46504</v>
       </c>
     </row>
     <row r="16">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46004</v>
+        <v>46323</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46186</v>
+        <v>46505</v>
       </c>
     </row>
     <row r="8">
